--- a/business_forms/040_production_closure_checklist--business_forms.xlsx
+++ b/business_forms/040_production_closure_checklist--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,14 +528,10 @@
           <t>Production Site</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -558,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -581,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -601,14 +597,10 @@
           <t>Production Location</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -631,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -654,7 +646,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -677,7 +669,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -700,7 +692,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -723,7 +715,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -746,7 +738,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -769,7 +761,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -792,7 +784,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -809,289 +801,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Production Review</t>
+          <t>Production Status</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Production Status</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Production Comments</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Production Photos</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Production Videos</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Production Files</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Production Notes</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Production Review</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Production Status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Production Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Production Photos</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Production Videos</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Production Files</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1106,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -1173,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>indoor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Indoor</t>
         </is>
       </c>
     </row>
@@ -1190,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>outdoor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Outdoor</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1360,44 +1076,10 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_14_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>production_closure_checklist_14_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
